--- a/InputData/trans/BLP/BAU LCFS Perc.xlsx
+++ b/InputData/trans/BLP/BAU LCFS Perc.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10526"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shigu\Documents\_swj\_Talanoa\CPSA Fletcher\dados\InputData (BR) 2024\d17 trans\BLP\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ssy02/Desktop/Postdoc Projects/eps-brazil-cpl/InputData/trans/BLP/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1824223-DE62-4CEB-B60C-62251343CDB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28D43126-B16C-6F40-82B4-67652A66877E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3552" yWindow="2256" windowWidth="19512" windowHeight="9912" firstSheet="2" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="34200" windowHeight="21380" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AboutX" sheetId="1" r:id="rId1"/>
@@ -402,9 +402,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
-    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="0.0000"/>
-    <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="0.0000"/>
+    <numFmt numFmtId="166" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="30" x14ac:knownFonts="1">
     <font>
@@ -1102,7 +1102,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" applyNumberFormat="0" applyFont="0" applyProtection="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="36">
@@ -1111,7 +1111,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1121,10 +1121,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="35" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="35" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1139,13 +1139,13 @@
     </xf>
     <xf numFmtId="0" fontId="21" fillId="37" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="21" fillId="37" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="21" fillId="37" borderId="15" xfId="63" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="21" fillId="0" borderId="0" xfId="63" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="21" fillId="37" borderId="15" xfId="63" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="21" fillId="0" borderId="0" xfId="63" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="15" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="21" fillId="0" borderId="15" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="21" fillId="0" borderId="15" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="38" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="38" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1164,71 +1164,71 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="65">
+    <cellStyle name="20% - Accent1" xfId="25" builtinId="30" customBuiltin="1"/>
     <cellStyle name="20% - Accent1 2" xfId="50" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="20% - Accent2" xfId="28" builtinId="34" customBuiltin="1"/>
     <cellStyle name="20% - Accent2 2" xfId="52" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
+    <cellStyle name="20% - Accent3" xfId="31" builtinId="38" customBuiltin="1"/>
     <cellStyle name="20% - Accent3 2" xfId="54" xr:uid="{00000000-0005-0000-0000-000005000000}"/>
+    <cellStyle name="20% - Accent4" xfId="34" builtinId="42" customBuiltin="1"/>
     <cellStyle name="20% - Accent4 2" xfId="56" xr:uid="{00000000-0005-0000-0000-000007000000}"/>
+    <cellStyle name="20% - Accent5" xfId="37" builtinId="46" customBuiltin="1"/>
     <cellStyle name="20% - Accent5 2" xfId="58" xr:uid="{00000000-0005-0000-0000-000009000000}"/>
+    <cellStyle name="20% - Accent6" xfId="40" builtinId="50" customBuiltin="1"/>
     <cellStyle name="20% - Accent6 2" xfId="60" xr:uid="{00000000-0005-0000-0000-00000B000000}"/>
-    <cellStyle name="20% - Ênfase1" xfId="25" builtinId="30" customBuiltin="1"/>
-    <cellStyle name="20% - Ênfase2" xfId="28" builtinId="34" customBuiltin="1"/>
-    <cellStyle name="20% - Ênfase3" xfId="31" builtinId="38" customBuiltin="1"/>
-    <cellStyle name="20% - Ênfase4" xfId="34" builtinId="42" customBuiltin="1"/>
-    <cellStyle name="20% - Ênfase5" xfId="37" builtinId="46" customBuiltin="1"/>
-    <cellStyle name="20% - Ênfase6" xfId="40" builtinId="50" customBuiltin="1"/>
+    <cellStyle name="40% - Accent1" xfId="26" builtinId="31" customBuiltin="1"/>
     <cellStyle name="40% - Accent1 2" xfId="51" xr:uid="{00000000-0005-0000-0000-00000D000000}"/>
+    <cellStyle name="40% - Accent2" xfId="29" builtinId="35" customBuiltin="1"/>
     <cellStyle name="40% - Accent2 2" xfId="53" xr:uid="{00000000-0005-0000-0000-00000F000000}"/>
+    <cellStyle name="40% - Accent3" xfId="32" builtinId="39" customBuiltin="1"/>
     <cellStyle name="40% - Accent3 2" xfId="55" xr:uid="{00000000-0005-0000-0000-000011000000}"/>
+    <cellStyle name="40% - Accent4" xfId="35" builtinId="43" customBuiltin="1"/>
     <cellStyle name="40% - Accent4 2" xfId="57" xr:uid="{00000000-0005-0000-0000-000013000000}"/>
+    <cellStyle name="40% - Accent5" xfId="38" builtinId="47" customBuiltin="1"/>
     <cellStyle name="40% - Accent5 2" xfId="59" xr:uid="{00000000-0005-0000-0000-000015000000}"/>
+    <cellStyle name="40% - Accent6" xfId="41" builtinId="51" customBuiltin="1"/>
     <cellStyle name="40% - Accent6 2" xfId="61" xr:uid="{00000000-0005-0000-0000-000017000000}"/>
-    <cellStyle name="40% - Ênfase1" xfId="26" builtinId="31" customBuiltin="1"/>
-    <cellStyle name="40% - Ênfase2" xfId="29" builtinId="35" customBuiltin="1"/>
-    <cellStyle name="40% - Ênfase3" xfId="32" builtinId="39" customBuiltin="1"/>
-    <cellStyle name="40% - Ênfase4" xfId="35" builtinId="43" customBuiltin="1"/>
-    <cellStyle name="40% - Ênfase5" xfId="38" builtinId="47" customBuiltin="1"/>
-    <cellStyle name="40% - Ênfase6" xfId="41" builtinId="51" customBuiltin="1"/>
     <cellStyle name="60% - Accent1 2" xfId="43" xr:uid="{00000000-0005-0000-0000-000018000000}"/>
     <cellStyle name="60% - Accent2 2" xfId="44" xr:uid="{00000000-0005-0000-0000-000019000000}"/>
     <cellStyle name="60% - Accent3 2" xfId="45" xr:uid="{00000000-0005-0000-0000-00001A000000}"/>
     <cellStyle name="60% - Accent4 2" xfId="46" xr:uid="{00000000-0005-0000-0000-00001B000000}"/>
     <cellStyle name="60% - Accent5 2" xfId="47" xr:uid="{00000000-0005-0000-0000-00001C000000}"/>
     <cellStyle name="60% - Accent6 2" xfId="48" xr:uid="{00000000-0005-0000-0000-00001D000000}"/>
+    <cellStyle name="Accent1" xfId="24" builtinId="29" customBuiltin="1"/>
+    <cellStyle name="Accent2" xfId="27" builtinId="33" customBuiltin="1"/>
+    <cellStyle name="Accent3" xfId="30" builtinId="37" customBuiltin="1"/>
+    <cellStyle name="Accent4" xfId="33" builtinId="41" customBuiltin="1"/>
+    <cellStyle name="Accent5" xfId="36" builtinId="45" customBuiltin="1"/>
+    <cellStyle name="Accent6" xfId="39" builtinId="49" customBuiltin="1"/>
+    <cellStyle name="Bad" xfId="14" builtinId="27" customBuiltin="1"/>
     <cellStyle name="Body: normal cell" xfId="4" xr:uid="{00000000-0005-0000-0000-000025000000}"/>
     <cellStyle name="Body: normal cell 2" xfId="62" xr:uid="{00000000-0005-0000-0000-000026000000}"/>
-    <cellStyle name="Bom" xfId="13" builtinId="26" customBuiltin="1"/>
-    <cellStyle name="Cálculo" xfId="17" builtinId="22" customBuiltin="1"/>
-    <cellStyle name="Célula de Verificação" xfId="19" builtinId="23" customBuiltin="1"/>
-    <cellStyle name="Célula Vinculada" xfId="18" builtinId="24" customBuiltin="1"/>
-    <cellStyle name="Ênfase1" xfId="24" builtinId="29" customBuiltin="1"/>
-    <cellStyle name="Ênfase2" xfId="27" builtinId="33" customBuiltin="1"/>
-    <cellStyle name="Ênfase3" xfId="30" builtinId="37" customBuiltin="1"/>
-    <cellStyle name="Ênfase4" xfId="33" builtinId="41" customBuiltin="1"/>
-    <cellStyle name="Ênfase5" xfId="36" builtinId="45" customBuiltin="1"/>
-    <cellStyle name="Ênfase6" xfId="39" builtinId="49" customBuiltin="1"/>
-    <cellStyle name="Entrada" xfId="15" builtinId="20" customBuiltin="1"/>
+    <cellStyle name="Calculation" xfId="17" builtinId="22" customBuiltin="1"/>
+    <cellStyle name="Check Cell" xfId="19" builtinId="23" customBuiltin="1"/>
+    <cellStyle name="Comma" xfId="63" builtinId="3"/>
+    <cellStyle name="Explanatory Text" xfId="22" builtinId="53" customBuiltin="1"/>
     <cellStyle name="Font: Calibri, 9pt regular" xfId="6" xr:uid="{00000000-0005-0000-0000-00002A000000}"/>
     <cellStyle name="Footnotes: top row" xfId="2" xr:uid="{00000000-0005-0000-0000-00002B000000}"/>
+    <cellStyle name="Good" xfId="13" builtinId="26" customBuiltin="1"/>
     <cellStyle name="Header: bottom row" xfId="5" xr:uid="{00000000-0005-0000-0000-00002D000000}"/>
-    <cellStyle name="Hiperlink" xfId="64" builtinId="8"/>
+    <cellStyle name="Heading 1" xfId="9" builtinId="16" customBuiltin="1"/>
+    <cellStyle name="Heading 2" xfId="10" builtinId="17" customBuiltin="1"/>
+    <cellStyle name="Heading 3" xfId="11" builtinId="18" customBuiltin="1"/>
+    <cellStyle name="Heading 4" xfId="12" builtinId="19" customBuiltin="1"/>
+    <cellStyle name="Hyperlink" xfId="64" builtinId="8"/>
+    <cellStyle name="Input" xfId="15" builtinId="20" customBuiltin="1"/>
+    <cellStyle name="Linked Cell" xfId="18" builtinId="24" customBuiltin="1"/>
     <cellStyle name="Neutral 2" xfId="42" xr:uid="{00000000-0005-0000-0000-000034000000}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000036000000}"/>
-    <cellStyle name="Nota" xfId="21" builtinId="10" customBuiltin="1"/>
+    <cellStyle name="Note" xfId="21" builtinId="10" customBuiltin="1"/>
     <cellStyle name="Note 2" xfId="49" xr:uid="{00000000-0005-0000-0000-000038000000}"/>
+    <cellStyle name="Output" xfId="16" builtinId="21" customBuiltin="1"/>
     <cellStyle name="Parent row" xfId="3" xr:uid="{00000000-0005-0000-0000-00003A000000}"/>
-    <cellStyle name="Ruim" xfId="14" builtinId="27" customBuiltin="1"/>
-    <cellStyle name="Saída" xfId="16" builtinId="21" customBuiltin="1"/>
     <cellStyle name="Table title" xfId="7" xr:uid="{00000000-0005-0000-0000-00003B000000}"/>
-    <cellStyle name="Texto de Aviso" xfId="20" builtinId="11" customBuiltin="1"/>
-    <cellStyle name="Texto Explicativo" xfId="22" builtinId="53" customBuiltin="1"/>
-    <cellStyle name="Título" xfId="8" builtinId="15" customBuiltin="1"/>
-    <cellStyle name="Título 1" xfId="9" builtinId="16" customBuiltin="1"/>
-    <cellStyle name="Título 2" xfId="10" builtinId="17" customBuiltin="1"/>
-    <cellStyle name="Título 3" xfId="11" builtinId="18" customBuiltin="1"/>
-    <cellStyle name="Título 4" xfId="12" builtinId="19" customBuiltin="1"/>
+    <cellStyle name="Title" xfId="8" builtinId="15" customBuiltin="1"/>
     <cellStyle name="Total" xfId="23" builtinId="25" customBuiltin="1"/>
-    <cellStyle name="Vírgula" xfId="63" builtinId="3"/>
+    <cellStyle name="Warning Text" xfId="20" builtinId="11" customBuiltin="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1575,17 +1575,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B12"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="56.77734375" customWidth="1"/>
+    <col min="2" max="2" width="56.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -1593,37 +1593,37 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -1637,17 +1637,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E557B04-A49A-4985-A344-B3E6E7915F28}">
   <dimension ref="A1:B43"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="170.109375" customWidth="1"/>
+    <col min="2" max="2" width="170.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -1655,171 +1655,171 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B4" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B5" s="5">
         <v>2017</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B6" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B7" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B8" s="6" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B9" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B10" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B12" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B13" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" s="1"/>
       <c r="B14" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" s="1"/>
       <c r="B15" s="6" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16" s="1"/>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B17" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B18" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B19" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B20" s="6" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" s="1"/>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B23" s="4" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B24" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B25" s="5">
         <v>2010</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B26" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B27" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B28" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B30" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B31" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B32" s="5">
         <v>2010</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B33" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B34" s="6" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A37" s="1"/>
       <c r="B37" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A38" s="1"/>
       <c r="B38" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A39" s="1"/>
       <c r="B39" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="40" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="41" spans="1:2" ht="0.9" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="42" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="43" spans="1:2" ht="0.9" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="40" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="41" spans="1:2" ht="1" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="42" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="43" spans="1:2" ht="1" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="B15" r:id="rId1" xr:uid="{DE198AB6-20A9-4C8B-9773-036C809CCA7F}"/>
@@ -1838,93 +1838,93 @@
     <tabColor rgb="FF92D050"/>
   </sheetPr>
   <dimension ref="A1:AK32"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="68.44140625" customWidth="1"/>
-    <col min="2" max="2" width="27.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="68.5" customWidth="1"/>
+    <col min="2" max="2" width="27.5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="18" bestFit="1" customWidth="1"/>
     <col min="4" max="38" width="15.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A6" s="5"/>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="17" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="18" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="19" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="22" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B22" s="7">
         <v>2015</v>
       </c>
@@ -2034,7 +2034,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="23" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A23" s="8" t="s">
         <v>52</v>
       </c>
@@ -2183,7 +2183,7 @@
         <v>0.39193533293914995</v>
       </c>
     </row>
-    <row r="24" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A24" s="10" t="s">
         <v>53</v>
       </c>
@@ -2332,7 +2332,7 @@
         <v>0.53051261994333521</v>
       </c>
     </row>
-    <row r="25" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A25" s="10" t="s">
         <v>54</v>
       </c>
@@ -2445,7 +2445,7 @@
         <v>0.20000000000000009</v>
       </c>
     </row>
-    <row r="26" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A26" s="10" t="s">
         <v>55</v>
       </c>
@@ -2558,7 +2558,7 @@
         <v>0.20000000000000009</v>
       </c>
     </row>
-    <row r="28" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A28" s="13" t="s">
         <v>56</v>
       </c>
@@ -2707,7 +2707,7 @@
         <v>0.19596766646957497</v>
       </c>
     </row>
-    <row r="32" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B32" s="11"/>
     </row>
   </sheetData>
@@ -2719,31 +2719,31 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9C93AE9-E2E3-4CC1-B360-81105BF9E042}">
   <dimension ref="A1:AL44"/>
-  <sheetFormatPr defaultColWidth="9.33203125" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.33203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="28.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="28.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="22.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="10" width="15.33203125" bestFit="1" customWidth="1"/>
     <col min="11" max="38" width="16.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="2" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A2" s="14" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="4" spans="1:38" s="17" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:38" s="17" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A4" s="15" t="s">
         <v>59</v>
       </c>
       <c r="B4" s="16"/>
     </row>
-    <row r="5" spans="1:38" s="19" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:38" s="19" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A5" s="18" t="s">
         <v>60</v>
       </c>
@@ -2859,7 +2859,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="6" spans="1:38" s="19" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:38" s="19" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A6" s="20" t="s">
         <v>62</v>
       </c>
@@ -2975,7 +2975,7 @@
         <v>2545447534.5174518</v>
       </c>
     </row>
-    <row r="7" spans="1:38" s="19" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:38" s="19" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A7" s="20" t="s">
         <v>62</v>
       </c>
@@ -3091,7 +3091,7 @@
         <v>520937.47106026468</v>
       </c>
     </row>
-    <row r="8" spans="1:38" s="19" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:38" s="19" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A8" s="20" t="s">
         <v>62</v>
       </c>
@@ -3207,7 +3207,7 @@
         <v>20017480491.667511</v>
       </c>
     </row>
-    <row r="9" spans="1:38" s="19" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:38" s="19" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A9" s="20" t="s">
         <v>62</v>
       </c>
@@ -3323,7 +3323,7 @@
         <v>16509486427.274775</v>
       </c>
     </row>
-    <row r="10" spans="1:38" s="19" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:38" s="19" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A10" s="20" t="s">
         <v>62</v>
       </c>
@@ -3439,7 +3439,7 @@
         <v>447886842.89772946</v>
       </c>
     </row>
-    <row r="11" spans="1:38" s="19" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:38" s="19" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A11" s="20" t="s">
         <v>62</v>
       </c>
@@ -3555,7 +3555,7 @@
         <v>19365649828.459015</v>
       </c>
     </row>
-    <row r="12" spans="1:38" s="19" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:38" s="19" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A12" s="20" t="s">
         <v>62</v>
       </c>
@@ -3671,7 +3671,7 @@
         <v>11912315692.799999</v>
       </c>
     </row>
-    <row r="13" spans="1:38" s="19" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:38" s="19" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A13" s="20" t="s">
         <v>62</v>
       </c>
@@ -3787,7 +3787,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:38" s="19" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:38" s="19" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A14" s="20" t="s">
         <v>62</v>
       </c>
@@ -3903,7 +3903,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:38" s="19" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:38" s="19" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A15" s="20" t="s">
         <v>62</v>
       </c>
@@ -4019,7 +4019,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:38" s="19" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:38" s="19" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A16" s="20" t="s">
         <v>62</v>
       </c>
@@ -4135,7 +4135,7 @@
         <v>3525155958.4000006</v>
       </c>
     </row>
-    <row r="17" spans="1:38" s="19" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:38" s="19" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A17" s="20" t="s">
         <v>74</v>
       </c>
@@ -4251,7 +4251,7 @@
         <v>5386302376.5572815</v>
       </c>
     </row>
-    <row r="18" spans="1:38" s="19" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:38" s="19" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A18" s="20" t="s">
         <v>74</v>
       </c>
@@ -4367,7 +4367,7 @@
         <v>2782978280.1198249</v>
       </c>
     </row>
-    <row r="19" spans="1:38" s="19" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:38" s="19" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A19" s="20" t="s">
         <v>74</v>
       </c>
@@ -4483,7 +4483,7 @@
         <v>1758552702.7772868</v>
       </c>
     </row>
-    <row r="20" spans="1:38" s="19" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:38" s="19" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A20" s="20" t="s">
         <v>75</v>
       </c>
@@ -4599,7 +4599,7 @@
         <v>5054881539.5416737</v>
       </c>
     </row>
-    <row r="21" spans="1:38" s="19" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:38" s="19" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A21" s="20" t="s">
         <v>75</v>
       </c>
@@ -4715,7 +4715,7 @@
         <v>30323.971594334187</v>
       </c>
     </row>
-    <row r="22" spans="1:38" s="19" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:38" s="19" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A22" s="20" t="s">
         <v>76</v>
       </c>
@@ -4831,7 +4831,7 @@
         <v>12528430342.711115</v>
       </c>
     </row>
-    <row r="23" spans="1:38" s="19" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:38" s="19" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A23" s="20" t="s">
         <v>75</v>
       </c>
@@ -4947,7 +4947,7 @@
         <v>7880625282.8919907</v>
       </c>
     </row>
-    <row r="24" spans="1:38" s="19" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:38" s="19" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A24" s="20" t="s">
         <v>77</v>
       </c>
@@ -5063,7 +5063,7 @@
         <v>9780609306.3001728</v>
       </c>
     </row>
-    <row r="25" spans="1:38" s="19" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:38" s="19" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A25" s="20" t="s">
         <v>79</v>
       </c>
@@ -5179,7 +5179,7 @@
         <v>14623829956.372179</v>
       </c>
     </row>
-    <row r="26" spans="1:38" s="19" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:38" s="19" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A26" s="20" t="s">
         <v>80</v>
       </c>
@@ -5295,7 +5295,7 @@
         <v>3104178008.1578941</v>
       </c>
     </row>
-    <row r="27" spans="1:38" s="19" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:38" s="19" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A27" s="20" t="s">
         <v>81</v>
       </c>
@@ -5411,7 +5411,7 @@
         <v>3451259678.6666665</v>
       </c>
     </row>
-    <row r="28" spans="1:38" s="17" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:38" s="17" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C28" s="22"/>
       <c r="D28" s="22"/>
       <c r="E28" s="22"/>
@@ -5434,7 +5434,7 @@
       <c r="V28" s="22"/>
       <c r="W28" s="22"/>
     </row>
-    <row r="29" spans="1:38" s="17" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:38" s="17" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C29" s="22"/>
       <c r="D29" s="22"/>
       <c r="E29" s="22"/>
@@ -5457,8 +5457,8 @@
       <c r="V29" s="22"/>
       <c r="W29" s="22"/>
     </row>
-    <row r="30" spans="1:38" s="17" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="31" spans="1:38" s="17" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:38" s="17" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="31" spans="1:38" s="17" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B31" s="23" t="s">
         <v>82</v>
       </c>
@@ -5571,7 +5571,7 @@
         <v>38061531367.186707</v>
       </c>
     </row>
-    <row r="32" spans="1:38" s="17" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:38" s="17" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B32" s="25" t="s">
         <v>83</v>
       </c>
@@ -5684,7 +5684,7 @@
         <v>67681170393.573875</v>
       </c>
     </row>
-    <row r="33" spans="2:38" s="17" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:38" s="17" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B33" s="25" t="s">
         <v>84</v>
       </c>
@@ -5797,7 +5797,7 @@
         <v>30959876949.496914</v>
       </c>
     </row>
-    <row r="34" spans="2:38" s="17" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:38" s="17" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B34" s="25" t="s">
         <v>85</v>
       </c>
@@ -5910,7 +5910,7 @@
         <v>447886842.89772946</v>
       </c>
     </row>
-    <row r="35" spans="2:38" s="17" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:38" s="17" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B35" s="25" t="s">
         <v>86</v>
       </c>
@@ -6023,7 +6023,7 @@
         <v>3525155958.4000006</v>
       </c>
     </row>
-    <row r="36" spans="2:38" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B36" s="26" t="s">
         <v>87</v>
       </c>
@@ -6172,12 +6172,12 @@
         <v>140675621511.55524</v>
       </c>
     </row>
-    <row r="38" spans="2:38" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B38" s="28" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="39" spans="2:38" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B39" s="23" t="s">
         <v>82</v>
       </c>
@@ -6326,7 +6326,7 @@
         <v>10054790864.332447</v>
       </c>
     </row>
-    <row r="40" spans="2:38" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B40" s="25" t="s">
         <v>83</v>
       </c>
@@ -6475,7 +6475,7 @@
         <v>17879470145.211201</v>
       </c>
     </row>
-    <row r="41" spans="2:38" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B41" s="25" t="s">
         <v>84</v>
       </c>
@@ -6624,7 +6624,7 @@
         <v>8178732613.5024996</v>
       </c>
     </row>
-    <row r="42" spans="2:38" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B42" s="25" t="s">
         <v>85</v>
       </c>
@@ -6773,7 +6773,7 @@
         <v>118319163.061979</v>
       </c>
     </row>
-    <row r="43" spans="2:38" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B43" s="25" t="s">
         <v>86</v>
       </c>
@@ -6922,7 +6922,7 @@
         <v>931247499.84244502</v>
       </c>
     </row>
-    <row r="44" spans="2:38" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B44" s="26" t="s">
         <v>87</v>
       </c>
@@ -7079,32 +7079,32 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3475F9D-B796-4455-9F8D-6BAC88AC929D}">
   <dimension ref="A1:AN44"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="26.6640625" style="30" customWidth="1"/>
     <col min="2" max="2" width="14.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="40" width="15.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="2" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A2" s="14" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="5" spans="1:40" s="28" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:40" s="28" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A5" s="29" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="6" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A6"/>
     </row>
-    <row r="7" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:40" x14ac:dyDescent="0.2">
       <c r="B7">
         <v>2012</v>
       </c>
@@ -7223,7 +7223,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="8" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A8" s="31" t="s">
         <v>90</v>
       </c>
@@ -7345,7 +7345,7 @@
         <v>0.20000000000000009</v>
       </c>
     </row>
-    <row r="9" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A9" s="32" t="s">
         <v>91</v>
       </c>
@@ -7467,7 +7467,7 @@
         <v>45036412.462165937</v>
       </c>
     </row>
-    <row r="10" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A10" s="32" t="s">
         <v>92</v>
       </c>
@@ -7628,110 +7628,110 @@
         <v>11897359152.955301</v>
       </c>
     </row>
-    <row r="11" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A11"/>
     </row>
-    <row r="12" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A12"/>
     </row>
-    <row r="13" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A13"/>
     </row>
-    <row r="14" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A14"/>
     </row>
-    <row r="15" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A15"/>
     </row>
-    <row r="16" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A16"/>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A17"/>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A18"/>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A19"/>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A20"/>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A21"/>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A22"/>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A23"/>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A24"/>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A25"/>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A26"/>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A27"/>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A28"/>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A29"/>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A30"/>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A31"/>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A32"/>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A33"/>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A34"/>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35"/>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A36"/>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A37"/>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A38"/>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A39"/>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A40"/>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A41"/>
     </row>
-    <row r="42" spans="1:3" s="33" customFormat="1" ht="18" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:3" s="33" customFormat="1" ht="19" x14ac:dyDescent="0.25">
       <c r="A42"/>
       <c r="B42"/>
       <c r="C42"/>
     </row>
-    <row r="43" spans="1:3" s="33" customFormat="1" ht="18" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:3" s="33" customFormat="1" ht="19" x14ac:dyDescent="0.25">
       <c r="A43"/>
       <c r="B43"/>
       <c r="C43"/>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A44"/>
     </row>
   </sheetData>
@@ -7742,7 +7742,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59C8B9D5-A333-4541-A2FA-721D42F40A7B}">
   <dimension ref="A2:D30"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
     <col min="2" max="4" width="34.6640625" bestFit="1" customWidth="1"/>
@@ -7750,22 +7750,22 @@
     <col min="6" max="6" width="6.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A27" s="34" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A28" s="5" t="s">
         <v>94</v>
       </c>
@@ -7779,7 +7779,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A29" s="5" t="s">
         <v>98</v>
       </c>
@@ -7793,7 +7793,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A30" s="5" t="s">
         <v>102</v>
       </c>
@@ -7812,27 +7812,27 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{989510D9-D9AF-490E-9EA8-CD6CEE602067}">
   <dimension ref="A2:B17"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="32.6640625" customWidth="1"/>
     <col min="2" max="2" width="26.6640625" customWidth="1"/>
-    <col min="3" max="3" width="25.44140625" customWidth="1"/>
+    <col min="3" max="3" width="25.5" customWidth="1"/>
     <col min="4" max="4" width="23.6640625" customWidth="1"/>
-    <col min="5" max="5" width="19.5546875" customWidth="1"/>
+    <col min="5" max="5" width="19.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
         <v>104</v>
       </c>
       <c r="B2" s="4"/>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" s="34" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>106</v>
       </c>
@@ -7840,7 +7840,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>107</v>
       </c>
@@ -7848,7 +7848,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>108</v>
       </c>
@@ -7856,7 +7856,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>109</v>
       </c>
@@ -7864,12 +7864,12 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>111</v>
       </c>
@@ -7878,22 +7878,22 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" s="34" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>115</v>
       </c>
@@ -7906,24 +7906,24 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24FCD0A5-CD11-4AB5-A5A1-9710443D6D95}">
   <dimension ref="A1:A5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A2" s="5">
         <v>0.26417200000000002</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>1000</v>
       </c>
@@ -7939,12 +7939,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AJ2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="15.88671875" customWidth="1"/>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:36" x14ac:dyDescent="0.2">
       <c r="B1">
         <v>2020</v>
       </c>
@@ -8039,133 +8039,102 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:36" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:36" ht="32" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B2" s="3">
-        <f>Calsc!G28</f>
-        <v>0.17290958078619265</v>
+        <v>0</v>
       </c>
       <c r="C2" s="3">
-        <f>Calsc!H28</f>
-        <v>0.17538958936214122</v>
+        <v>0</v>
       </c>
       <c r="D2" s="3">
-        <f>Calsc!I28</f>
-        <v>0.17769037324490353</v>
+        <v>0</v>
       </c>
       <c r="E2" s="3">
-        <f>Calsc!J28</f>
-        <v>0.18015662542123334</v>
+        <v>0</v>
       </c>
       <c r="F2" s="3">
-        <f>Calsc!K28</f>
-        <v>0.18281429923763298</v>
+        <v>0</v>
       </c>
       <c r="G2" s="3">
-        <f>Calsc!L28</f>
-        <v>0.18545292431646906</v>
+        <v>0</v>
       </c>
       <c r="H2" s="3">
-        <f>Calsc!M28</f>
-        <v>0.18785835339598325</v>
+        <v>0</v>
       </c>
       <c r="I2" s="3">
-        <f>Calsc!N28</f>
-        <v>0.19005726982533233</v>
+        <v>0</v>
       </c>
       <c r="J2" s="3">
-        <f>Calsc!O28</f>
-        <v>0.19201690023181553</v>
+        <v>0</v>
       </c>
       <c r="K2" s="3">
-        <f>Calsc!P28</f>
-        <v>0.19379403413244611</v>
+        <v>0</v>
       </c>
       <c r="L2" s="3">
-        <f>Calsc!Q28</f>
-        <v>0.19539125548940017</v>
+        <v>0</v>
       </c>
       <c r="M2" s="3">
-        <f>Calsc!R28</f>
-        <v>0.19675068318360703</v>
+        <v>0</v>
       </c>
       <c r="N2" s="3">
-        <f>Calsc!S28</f>
-        <v>0.19787594302703224</v>
+        <v>0</v>
       </c>
       <c r="O2" s="3">
-        <f>Calsc!T28</f>
-        <v>0.19885340470217713</v>
+        <v>0</v>
       </c>
       <c r="P2" s="3">
-        <f>Calsc!U28</f>
-        <v>0.19954381420850528</v>
+        <v>0</v>
       </c>
       <c r="Q2" s="3">
-        <f>Calsc!V28</f>
-        <v>0.20003569769468443</v>
+        <v>0</v>
       </c>
       <c r="R2" s="3">
-        <f>Calsc!W28</f>
-        <v>0.20038848175531893</v>
+        <v>0</v>
       </c>
       <c r="S2" s="3">
-        <f>Calsc!X28</f>
-        <v>0.20059989313771409</v>
+        <v>0</v>
       </c>
       <c r="T2" s="3">
-        <f>Calsc!Y28</f>
-        <v>0.20080609389842941</v>
+        <v>0</v>
       </c>
       <c r="U2" s="3">
-        <f>Calsc!Z28</f>
-        <v>0.20083262784548062</v>
+        <v>0</v>
       </c>
       <c r="V2" s="3">
-        <f>Calsc!AA28</f>
-        <v>0.20077508707863256</v>
+        <v>0</v>
       </c>
       <c r="W2" s="3">
-        <f>Calsc!AB28</f>
-        <v>0.20062140340599671</v>
+        <v>0</v>
       </c>
       <c r="X2" s="3">
-        <f>Calsc!AC28</f>
-        <v>0.20037060459684938</v>
+        <v>0</v>
       </c>
       <c r="Y2" s="3">
-        <f>Calsc!AD28</f>
-        <v>0.20013082429254245</v>
+        <v>0</v>
       </c>
       <c r="Z2" s="3">
-        <f>Calsc!AE28</f>
-        <v>0.19966575178466875</v>
+        <v>0</v>
       </c>
       <c r="AA2" s="3">
-        <f>Calsc!AF28</f>
-        <v>0.19907821707476317</v>
+        <v>0</v>
       </c>
       <c r="AB2" s="3">
-        <f>Calsc!AG28</f>
-        <v>0.19839750056084832</v>
+        <v>0</v>
       </c>
       <c r="AC2" s="3">
-        <f>Calsc!AH28</f>
-        <v>0.19765020543712006</v>
+        <v>0</v>
       </c>
       <c r="AD2" s="3">
-        <f>Calsc!AI28</f>
-        <v>0.19703966300149092</v>
+        <v>0</v>
       </c>
       <c r="AE2" s="3">
-        <f>Calsc!AJ28</f>
-        <v>0.19634722931226326</v>
+        <v>0</v>
       </c>
       <c r="AF2" s="3">
-        <f>Calsc!AK28</f>
-        <v>0.19596766646957497</v>
+        <v>0</v>
       </c>
       <c r="AG2" s="3"/>
       <c r="AH2" s="3"/>
